--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>GFAI</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43281</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E8" s="3">
         <v>18400</v>
       </c>
-      <c r="E8" s="3">
-        <v>34500</v>
-      </c>
       <c r="F8" s="3">
+        <v>34000</v>
+      </c>
+      <c r="G8" s="3">
         <v>16900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>37300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2500</v>
       </c>
-      <c r="E10" s="3">
-        <v>4300</v>
-      </c>
       <c r="F10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,20 +924,23 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,14 +956,17 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1015,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E17" s="3">
         <v>30300</v>
       </c>
-      <c r="E17" s="3">
-        <v>51400</v>
-      </c>
       <c r="F17" s="3">
+        <v>50800</v>
+      </c>
+      <c r="G17" s="3">
         <v>22500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-16900</v>
-      </c>
       <c r="F18" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,101 +1107,108 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-10400</v>
+        <v>-13500</v>
       </c>
       <c r="E21" s="3">
-        <v>-12600</v>
+        <v>-10300</v>
       </c>
       <c r="F21" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-4000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1179,78 +1219,87 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-18700</v>
-      </c>
       <c r="F26" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13800</v>
       </c>
-      <c r="E27" s="3">
-        <v>-18600</v>
-      </c>
       <c r="F27" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,31 +1447,34 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1561,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43281</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,29 +1790,30 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E41" s="3">
         <v>24700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,8 +1826,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,29 +1864,32 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5700</v>
+        <v>6500</v>
       </c>
       <c r="E43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F43" s="3">
         <v>7300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,23 +1902,26 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1844,29 +1940,32 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10100</v>
+        <v>3900</v>
       </c>
       <c r="E45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F45" s="3">
         <v>16000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,29 +1978,32 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E46" s="3">
         <v>42200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1914,29 +2016,32 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="E47" s="3">
         <v>1900</v>
       </c>
       <c r="F47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G47" s="3">
         <v>2500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1949,29 +2054,32 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E48" s="3">
         <v>9300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,29 +2092,32 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E49" s="3">
         <v>8400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,29 +2206,32 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2800</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,29 +2282,32 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E54" s="3">
         <v>64100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>61200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2194,8 +2320,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,29 +2354,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2259,29 +2390,32 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E58" s="3">
         <v>7600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17500</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2294,29 +2428,32 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="E59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,29 +2466,32 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,29 +2504,32 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>17100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2399,29 +2542,32 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E62" s="3">
         <v>4800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2580,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,29 +2694,32 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E66" s="3">
         <v>39000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2732,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,29 +2900,32 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-16000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,8 +2938,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,29 +3052,32 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E76" s="3">
         <v>25100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +3090,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43281</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3038,34 +3237,37 @@
         <v>2600</v>
       </c>
       <c r="E83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3509,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3827,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>19900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E102" s="3">
         <v>17800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>GFAI</t>
   </si>
@@ -656,187 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>17900</v>
+        <v>8800</v>
       </c>
       <c r="E8" s="3">
-        <v>18400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>34000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>16900</v>
+        <v>8800</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>38600</v>
+        <v>9200</v>
       </c>
       <c r="I8" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>18600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>37300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>18900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
+        <v>15800</v>
+      </c>
+      <c r="L9" s="3">
+        <v>31500</v>
+      </c>
+      <c r="M9" s="3">
         <v>15000</v>
       </c>
-      <c r="E9" s="3">
-        <v>15900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>30200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>15000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>33900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>15800</v>
-      </c>
-      <c r="J9" s="3">
-        <v>31500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>15000</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2900</v>
+        <v>1600</v>
       </c>
       <c r="E10" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1900</v>
+        <v>1600</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
-        <v>4700</v>
+        <v>-300</v>
       </c>
       <c r="I10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +876,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +916,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,28 +960,34 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4400</v>
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1400</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -959,37 +998,43 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1003,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>35300</v>
+        <v>9800</v>
       </c>
       <c r="E17" s="3">
-        <v>30300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>50800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22500</v>
+        <v>9800</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
-        <v>38700</v>
+        <v>13400</v>
       </c>
       <c r="I17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>19200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>36100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>17900</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-17400</v>
+        <v>-1000</v>
       </c>
       <c r="E18" s="3">
-        <v>-11900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-16800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-5600</v>
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
-        <v>-100</v>
+        <v>-4200</v>
       </c>
       <c r="I18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,92 +1173,106 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1200</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-13500</v>
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
-        <v>-10300</v>
+        <v>-600</v>
       </c>
       <c r="F21" s="3">
-        <v>-12500</v>
+        <v>500</v>
       </c>
       <c r="G21" s="3">
+        <v>500</v>
+      </c>
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
-        <v>5400</v>
-      </c>
       <c r="I21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="3">
         <v>2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1201,20 +1280,20 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>300</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1222,84 +1301,102 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-16200</v>
+        <v>-1000</v>
       </c>
       <c r="E23" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-18500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6700</v>
+        <v>-1000</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
-        <v>100</v>
+        <v>-6500</v>
       </c>
       <c r="I23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>900</v>
-      </c>
-      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>400</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-15800</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-18600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-6300</v>
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>100</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-15800</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-18500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-6300</v>
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>100</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,37 +1565,43 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1488,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1200</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-15800</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-18600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-6300</v>
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>100</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-15800</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-18600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-6300</v>
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>100</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,35 +1962,37 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F41" s="3">
         <v>20200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>20200</v>
+      </c>
+      <c r="H41" s="3">
         <v>24700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="G41" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H41" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +2002,14 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,35 +2046,41 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6500</v>
+        <v>5600</v>
       </c>
       <c r="E43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F43" s="3">
         <v>6000</v>
       </c>
-      <c r="F43" s="3">
-        <v>7300</v>
-      </c>
       <c r="G43" s="3">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="3">
-        <v>5900</v>
+        <v>5400</v>
       </c>
       <c r="I43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K43" s="3">
         <v>6000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1905,32 +2090,38 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>400</v>
+      </c>
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
+        <v>500</v>
+      </c>
+      <c r="H44" s="3">
         <v>1600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J44" s="3">
         <v>5100</v>
       </c>
-      <c r="G44" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,35 +2134,41 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3900</v>
+        <v>600</v>
       </c>
       <c r="E45" s="3">
-        <v>9800</v>
+        <v>600</v>
       </c>
       <c r="F45" s="3">
-        <v>16000</v>
+        <v>3200</v>
       </c>
       <c r="G45" s="3">
-        <v>8900</v>
+        <v>3200</v>
       </c>
       <c r="H45" s="3">
-        <v>1400</v>
+        <v>8500</v>
       </c>
       <c r="I45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,35 +2178,41 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F46" s="3">
         <v>31100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>31100</v>
+      </c>
+      <c r="H46" s="3">
         <v>42200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>42200</v>
+      </c>
+      <c r="J46" s="3">
         <v>35300</v>
       </c>
-      <c r="G46" s="3">
-        <v>31900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>13400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,35 +2222,41 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>6500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2057,35 +2266,41 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F48" s="3">
         <v>6700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J48" s="3">
         <v>12200</v>
       </c>
-      <c r="G48" s="3">
-        <v>14400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,35 +2310,41 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H49" s="3">
         <v>8400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J49" s="3">
         <v>8500</v>
       </c>
-      <c r="G49" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>300</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2133,8 +2354,14 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,35 +2442,41 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="E52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="F52" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G52" s="3">
-        <v>11200</v>
+        <v>3600</v>
       </c>
       <c r="H52" s="3">
-        <v>3100</v>
+        <v>3600</v>
       </c>
       <c r="I52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K52" s="3">
         <v>2800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,8 +2486,14 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,35 +2530,41 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F54" s="3">
         <v>45800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>45800</v>
+      </c>
+      <c r="H54" s="3">
         <v>64100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>64100</v>
+      </c>
+      <c r="J54" s="3">
         <v>61200</v>
       </c>
-      <c r="G54" s="3">
-        <v>68800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>39300</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,8 +2574,14 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,13 +2614,15 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="E57" s="3">
         <v>2600</v>
@@ -2370,20 +2631,20 @@
         <v>2100</v>
       </c>
       <c r="G57" s="3">
-        <v>3700</v>
+        <v>2100</v>
       </c>
       <c r="H57" s="3">
-        <v>1700</v>
+        <v>2600</v>
       </c>
       <c r="I57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K57" s="3">
         <v>3100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,35 +2654,41 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>4800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J58" s="3">
         <v>10200</v>
       </c>
-      <c r="G58" s="3">
-        <v>18900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>23000</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>17500</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2431,35 +2698,41 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7100</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
-        <v>7000</v>
+        <v>800</v>
       </c>
       <c r="F59" s="3">
-        <v>6900</v>
+        <v>1200</v>
       </c>
       <c r="G59" s="3">
-        <v>7500</v>
+        <v>1200</v>
       </c>
       <c r="H59" s="3">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,35 +2742,41 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F60" s="3">
         <v>14000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="H60" s="3">
         <v>17200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J60" s="3">
         <v>19200</v>
       </c>
-      <c r="G60" s="3">
-        <v>30100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>26600</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>22600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2507,35 +2786,41 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="3">
         <v>17100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J61" s="3">
         <v>17900</v>
       </c>
-      <c r="G61" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2545,35 +2830,41 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>6100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2583,8 +2874,14 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,35 +3006,41 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20600</v>
+        <v>12600</v>
       </c>
       <c r="E66" s="3">
-        <v>39000</v>
+        <v>12600</v>
       </c>
       <c r="F66" s="3">
+        <v>20700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>20700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>39100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J66" s="3">
         <v>42000</v>
       </c>
-      <c r="G66" s="3">
-        <v>39400</v>
-      </c>
-      <c r="H66" s="3">
-        <v>38000</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>34900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +3050,14 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3200,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,35 +3244,41 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-57900</v>
+        <v>-60000</v>
       </c>
       <c r="E72" s="3">
-        <v>-42100</v>
+        <v>-60000</v>
       </c>
       <c r="F72" s="3">
-        <v>-28300</v>
+        <v>-58100</v>
       </c>
       <c r="G72" s="3">
-        <v>-16000</v>
+        <v>-58100</v>
       </c>
       <c r="H72" s="3">
-        <v>-1400</v>
+        <v>-42400</v>
       </c>
       <c r="I72" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3288,14 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,35 +3420,41 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F76" s="3">
         <v>25200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>25200</v>
+      </c>
+      <c r="H76" s="3">
         <v>25100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>25100</v>
+      </c>
+      <c r="J76" s="3">
         <v>19200</v>
       </c>
-      <c r="G76" s="3">
-        <v>29400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3464,14 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>43830</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-15800</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-18600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-6300</v>
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>100</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3623,54 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2700</v>
+        <v>1200</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
-        <v>5300</v>
+        <v>1300</v>
       </c>
       <c r="I83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-100</v>
+        <v>-900</v>
       </c>
       <c r="E89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-19200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-13800</v>
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
-        <v>5000</v>
+        <v>-500</v>
       </c>
       <c r="I89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3949,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4077,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1100</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-9300</v>
+        <v>100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
       </c>
       <c r="I94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +4143,33 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4315,142 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="E100" s="3">
-        <v>19900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>20900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>17400</v>
+        <v>-2200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
-        <v>-1700</v>
+        <v>9900</v>
       </c>
       <c r="I100" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-500</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>400</v>
+        <v>-300</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>100</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4100</v>
+        <v>-3200</v>
       </c>
       <c r="E102" s="3">
-        <v>17800</v>
+        <v>-3200</v>
       </c>
       <c r="F102" s="3">
-        <v>-7600</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-6300</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>2200</v>
+        <v>8900</v>
       </c>
       <c r="I102" s="3">
+        <v>8900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>GFAI</t>
   </si>
@@ -656,212 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F8" s="3">
         <v>8800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8800</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J8" s="3">
         <v>9200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9200</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>18600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>37300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>18900</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F9" s="3">
         <v>7200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7200</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J9" s="3">
         <v>9500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9500</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>15800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>31500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>15000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,16 +903,18 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -895,11 +922,11 @@
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,35 +999,41 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,44 +1043,50 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F17" s="3">
         <v>9800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9800</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="J17" s="3">
         <v>13400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>13400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>19200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>36100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>17900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-4200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4200</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,131 +1240,145 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
-        <v>500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1307,96 +1386,114 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1597,17 +1718,17 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3">
+        <v>600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,41 +2135,43 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F41" s="3">
         <v>14000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>14000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>20200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>24700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>24700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2181,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,41 +2231,47 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F43" s="3">
         <v>5600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,38 +2281,44 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>300</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2140,8 +2331,14 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2152,29 +2349,29 @@
         <v>600</v>
       </c>
       <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>600</v>
+      </c>
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>8500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>8500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>16600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,41 +2381,47 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F46" s="3">
         <v>22700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>31100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>42200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>42200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>35300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2431,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2254,15 +2463,15 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>6500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2272,41 +2481,47 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F48" s="3">
         <v>5900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>16400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,41 +2531,47 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F49" s="3">
         <v>3100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>8400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2360,8 +2581,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,22 +2681,28 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F52" s="3">
         <v>3400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3600</v>
       </c>
       <c r="H52" s="3">
         <v>3600</v>
@@ -2472,17 +2711,17 @@
         <v>3600</v>
       </c>
       <c r="J52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L52" s="3">
         <v>3700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,8 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,41 +2781,47 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>44700</v>
+      </c>
+      <c r="F54" s="3">
         <v>36200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>36200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>45800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>45800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>64100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>64100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>61200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2831,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,41 +2875,43 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2660,8 +2921,14 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2672,29 +2939,29 @@
         <v>1700</v>
       </c>
       <c r="F58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>10200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>17500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,41 +2971,47 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,41 +3021,47 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F60" s="3">
         <v>6600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>14000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>14000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>22600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,41 +3071,47 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>17100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>17100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>17900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2836,8 +3121,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2859,18 +3150,18 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>6100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3171,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,41 +3321,47 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F66" s="3">
         <v>12600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>20700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>20700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>39100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>39100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>42000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>34900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3371,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,41 +3591,47 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-60000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-60000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-58100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-58100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-42400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-42400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-28500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3641,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,41 +3791,47 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>32000</v>
+      </c>
+      <c r="F76" s="3">
         <v>23700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>23700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>25200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>25200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>25100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>25100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3841,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4020,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4390,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,22 +4536,28 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
@@ -4106,29 +4565,35 @@
       <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-500</v>
       </c>
       <c r="K94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,11 +4638,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2200</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J100" s="3">
         <v>9900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>9900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4376,81 +4873,93 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
-        <v>100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>400</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>400</v>
+      </c>
+      <c r="O101" s="3">
+        <v>100</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J102" s="3">
         <v>8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8900</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>GFAI</t>
   </si>
@@ -746,11 +746,11 @@
       <c r="E8" s="3">
         <v>9400</v>
       </c>
-      <c r="F8" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>8800</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>9100</v>
@@ -796,11 +796,11 @@
       <c r="E9" s="3">
         <v>7900</v>
       </c>
-      <c r="F9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>7200</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>7900</v>
@@ -846,11 +846,11 @@
       <c r="E10" s="3">
         <v>1500</v>
       </c>
-      <c r="F10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1600</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>1300</v>
@@ -1016,11 +1016,11 @@
       <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>3500</v>
@@ -1067,10 +1067,10 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
@@ -1133,11 +1133,11 @@
       <c r="E17" s="3">
         <v>11600</v>
       </c>
-      <c r="F17" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>9800</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>14400</v>
@@ -1183,11 +1183,11 @@
       <c r="E18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1000</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-5200</v>
@@ -1253,11 +1253,11 @@
       <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-600</v>
@@ -1304,10 +1304,10 @@
         <v>-1600</v>
       </c>
       <c r="F21" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-4100</v>
@@ -1353,11 +1353,11 @@
       <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1403,11 +1403,11 @@
       <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1000</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-8100</v>
@@ -1453,11 +1453,11 @@
       <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>-200</v>
@@ -1553,11 +1553,11 @@
       <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-7900</v>
@@ -1603,11 +1603,11 @@
       <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-7900</v>
@@ -1853,11 +1853,11 @@
       <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>100</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>600</v>
@@ -1903,11 +1903,11 @@
       <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-7900</v>
@@ -2003,11 +2003,11 @@
       <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-7900</v>
@@ -2148,11 +2148,11 @@
       <c r="E41" s="3">
         <v>21900</v>
       </c>
-      <c r="F41" s="3">
-        <v>14000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>14000</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>20200</v>
@@ -2248,11 +2248,11 @@
       <c r="E43" s="3">
         <v>6200</v>
       </c>
-      <c r="F43" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>5600</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>6000</v>
@@ -2298,11 +2298,11 @@
       <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="F44" s="3">
-        <v>400</v>
-      </c>
-      <c r="G44" s="3">
-        <v>400</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>500</v>
@@ -2348,11 +2348,11 @@
       <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
-        <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>3200</v>
@@ -2398,11 +2398,11 @@
       <c r="E46" s="3">
         <v>30800</v>
       </c>
-      <c r="F46" s="3">
-        <v>22700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>22700</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>31100</v>
@@ -2498,11 +2498,11 @@
       <c r="E48" s="3">
         <v>5500</v>
       </c>
-      <c r="F48" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5900</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>6700</v>
@@ -2548,11 +2548,11 @@
       <c r="E49" s="3">
         <v>2700</v>
       </c>
-      <c r="F49" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3100</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>3200</v>
@@ -2698,11 +2698,11 @@
       <c r="E52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3400</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>3600</v>
@@ -2798,11 +2798,11 @@
       <c r="E54" s="3">
         <v>44700</v>
       </c>
-      <c r="F54" s="3">
-        <v>36200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>36200</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>45800</v>
@@ -2888,11 +2888,11 @@
       <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2600</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>2100</v>
@@ -2938,11 +2938,11 @@
       <c r="E58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1700</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>4800</v>
@@ -2988,11 +2988,11 @@
       <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
-        <v>800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>800</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>1200</v>
@@ -3038,11 +3038,11 @@
       <c r="E60" s="3">
         <v>6300</v>
       </c>
-      <c r="F60" s="3">
-        <v>6600</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6600</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>14000</v>
@@ -3089,10 +3089,10 @@
         <v>900</v>
       </c>
       <c r="F61" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1700</v>
@@ -3338,11 +3338,11 @@
       <c r="E66" s="3">
         <v>12700</v>
       </c>
-      <c r="F66" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>12600</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>20700</v>
@@ -3608,11 +3608,11 @@
       <c r="E72" s="3">
         <v>-64000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-60000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-60000</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-58100</v>
@@ -3808,11 +3808,11 @@
       <c r="E76" s="3">
         <v>32000</v>
       </c>
-      <c r="F76" s="3">
-        <v>23700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>23700</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>25200</v>
@@ -3963,11 +3963,11 @@
       <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-7900</v>
@@ -4333,11 +4333,11 @@
       <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-900</v>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
@@ -4403,11 +4403,11 @@
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>-600</v>
@@ -4553,11 +4553,11 @@
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3">
-        <v>100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>100</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-500</v>
@@ -4823,11 +4823,11 @@
       <c r="E100" s="3">
         <v>4600</v>
       </c>
-      <c r="F100" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-2200</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>-1400</v>
@@ -4924,10 +4924,10 @@
         <v>4100</v>
       </c>
       <c r="F102" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-2200</v>

--- a/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>GFAI</t>
   </si>
@@ -656,215 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>9100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9100</v>
       </c>
-      <c r="F8" s="3">
-        <v>9400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9400</v>
-      </c>
       <c r="H8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J8" s="3">
         <v>8800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>18600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>37300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18900</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>7600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="L9" s="3">
         <v>7900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="M9" s="3">
         <v>7900</v>
       </c>
-      <c r="H9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>7900</v>
-      </c>
-      <c r="K9" s="3">
-        <v>7900</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>9500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>15800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>31500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>15000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1500</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>1500</v>
@@ -873,46 +892,52 @@
         <v>1500</v>
       </c>
       <c r="H10" s="3">
+        <v>800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>800</v>
+      </c>
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3900</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,16 +958,18 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>300</v>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F12" s="3">
         <v>300</v>
@@ -962,11 +989,11 @@
       <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
+      <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
+        <v>100</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
@@ -989,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,36 +1095,36 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1095,56 +1134,62 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1227,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
-        <v>11600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>11600</v>
-      </c>
       <c r="H17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>14400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>14400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>13400</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>19200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>36100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>17900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,120 +1375,134 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>500</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>500</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
-        <v>400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,44 +1512,44 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1478,120 +1557,138 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1852,17 +1973,17 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2115,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
-        <v>300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>300</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,53 +2482,55 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>24500</v>
+      </c>
+      <c r="F41" s="3">
         <v>23500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>23500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>21900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>21900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>14000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>20200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>20200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>24700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>24700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,16 +2540,22 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2423,53 +2602,59 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,16 +2664,22 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
@@ -2497,32 +2688,32 @@
         <v>300</v>
       </c>
       <c r="H44" s="3">
+        <v>300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>300</v>
+      </c>
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,22 +2726,28 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>600</v>
@@ -2559,29 +2756,29 @@
         <v>600</v>
       </c>
       <c r="J45" s="3">
+        <v>600</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>16600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,53 +2788,59 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F46" s="3">
         <v>31900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>31900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>30800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>30800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>22700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>22700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>31100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>31100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>42200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>42200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>35300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2850,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2685,15 +2894,15 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>6500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,53 +2912,59 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>16400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2759,53 +2974,59 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +3036,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,34 +3160,40 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3600</v>
       </c>
       <c r="L52" s="3">
         <v>3600</v>
@@ -2963,17 +3202,17 @@
         <v>3600</v>
       </c>
       <c r="N52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3222,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,53 +3284,59 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>49100</v>
+      </c>
+      <c r="F54" s="3">
         <v>47500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>47500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>44700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>44700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>36200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>45800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>45800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>64100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>64100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>61200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>36000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3346,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,53 +3398,55 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,22 +3456,28 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1700</v>
       </c>
       <c r="H58" s="3">
         <v>1700</v>
@@ -3219,29 +3486,29 @@
         <v>1700</v>
       </c>
       <c r="J58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L58" s="3">
         <v>4800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>10200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>17500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3251,53 +3518,59 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,53 +3580,59 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F60" s="3">
         <v>6100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>17200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>19200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>22600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,53 +3642,59 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>17100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>17100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>17900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3419,8 +3704,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3454,18 +3745,18 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>6100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3766,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,53 +3952,59 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F66" s="3">
         <v>13300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>13300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>20700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>39100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>39100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>42000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>34900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +4014,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,53 +4286,59 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-70600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-66200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-66200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-64000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-64000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-60000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-60000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-58100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-58100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-42400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-42400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-28500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4348,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,53 +4534,59 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>34200</v>
+      </c>
+      <c r="F76" s="3">
         <v>34300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>34300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>32000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>32000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>23700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>23700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>25200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>25200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>25100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>25100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>19200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1100</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4596,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4815,72 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>600</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-800</v>
-      </c>
       <c r="H89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5273,72 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,34 +5455,40 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-500</v>
       </c>
       <c r="L94" s="3">
         <v>-500</v>
@@ -5037,29 +5496,35 @@
       <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>-500</v>
       </c>
       <c r="O94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5118,11 +5585,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,72 +5789,84 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>9900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>9900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-3000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -5383,93 +5880,105 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
-        <v>100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>400</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>400</v>
+      </c>
+      <c r="S101" s="3">
+        <v>100</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>4100</v>
-      </c>
       <c r="H102" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8900</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
